--- a/Dataset_Lengkap_Proyek_ASA.xlsx
+++ b/Dataset_Lengkap_Proyek_ASA.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="15" documentId="11_2A5E2F57A3C78004374359350831BE96F2FCD08A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDA3FEFC-7F1C-43D3-BC33-A66FAE82273B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Hasil_Augmentasi" sheetId="1" r:id="rId1"/>
@@ -43910,5 +43910,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>